--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/78.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/78.xlsx
@@ -426,13 +426,13 @@
         <v>-23.70038438722496</v>
       </c>
       <c r="E2">
-        <v>-10.28755384668472</v>
+        <v>-9.271599760011892</v>
       </c>
       <c r="F2">
-        <v>-1.556357532812289</v>
+        <v>-1.541732706315864</v>
       </c>
       <c r="G2">
-        <v>-10.66941270518172</v>
+        <v>-9.861176117224048</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-23.1972709727479</v>
       </c>
       <c r="E3">
-        <v>-10.9928138601653</v>
+        <v>-10.27583415595287</v>
       </c>
       <c r="F3">
-        <v>-1.386318556039634</v>
+        <v>-1.743154382143577</v>
       </c>
       <c r="G3">
-        <v>-9.877447448549566</v>
+        <v>-9.593468852190883</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.69255715901264</v>
       </c>
       <c r="E4">
-        <v>-11.53812364322094</v>
+        <v>-10.90840310466232</v>
       </c>
       <c r="F4">
-        <v>-1.451120909593237</v>
+        <v>-1.712458399665439</v>
       </c>
       <c r="G4">
-        <v>-10.21641420631554</v>
+        <v>-9.473637035305883</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.23058449497125</v>
       </c>
       <c r="E5">
-        <v>-12.2629149650966</v>
+        <v>-12.0761154122802</v>
       </c>
       <c r="F5">
-        <v>-1.28743716753486</v>
+        <v>-1.529829895105038</v>
       </c>
       <c r="G5">
-        <v>-9.737583520606435</v>
+        <v>-9.73429945943148</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.79653335592857</v>
       </c>
       <c r="E6">
-        <v>-12.7887704238153</v>
+        <v>-11.68146795945974</v>
       </c>
       <c r="F6">
-        <v>-1.25554833599669</v>
+        <v>-1.589449153819324</v>
       </c>
       <c r="G6">
-        <v>-9.46315915867409</v>
+        <v>-9.063268431348906</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.41457118491701</v>
       </c>
       <c r="E7">
-        <v>-13.60755022372015</v>
+        <v>-13.94335921375895</v>
       </c>
       <c r="F7">
-        <v>-1.194017205316743</v>
+        <v>-1.557514762074</v>
       </c>
       <c r="G7">
-        <v>-9.135567435381049</v>
+        <v>-8.82836536206438</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.0614734697878</v>
       </c>
       <c r="E8">
-        <v>-14.75675918654269</v>
+        <v>-12.72712430714888</v>
       </c>
       <c r="F8">
-        <v>-1.105258466474179</v>
+        <v>-1.358574874985073</v>
       </c>
       <c r="G8">
-        <v>-8.929522391562349</v>
+        <v>-8.979286512108674</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.75082260391807</v>
       </c>
       <c r="E9">
-        <v>-14.79297792165604</v>
+        <v>-14.71204050571694</v>
       </c>
       <c r="F9">
-        <v>-1.32102166714656</v>
+        <v>-1.16517510908607</v>
       </c>
       <c r="G9">
-        <v>-9.013348715162236</v>
+        <v>-8.376085251580228</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.47154112219429</v>
       </c>
       <c r="E10">
-        <v>-15.79743421282339</v>
+        <v>-14.93579693490994</v>
       </c>
       <c r="F10">
-        <v>-1.019740300911366</v>
+        <v>-1.262608511370751</v>
       </c>
       <c r="G10">
-        <v>-8.805383554930758</v>
+        <v>-8.280195300035238</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.20515941467962</v>
       </c>
       <c r="E11">
-        <v>-16.38797439426765</v>
+        <v>-15.82214609548325</v>
       </c>
       <c r="F11">
-        <v>-0.9679747935430224</v>
+        <v>-1.058053950025649</v>
       </c>
       <c r="G11">
-        <v>-8.183596891744845</v>
+        <v>-7.729224516479874</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-19.9629832962421</v>
       </c>
       <c r="E12">
-        <v>-16.87112634309402</v>
+        <v>-16.08870113252274</v>
       </c>
       <c r="F12">
-        <v>-0.7113581692993748</v>
+        <v>-1.116199543130355</v>
       </c>
       <c r="G12">
-        <v>-7.880993166182222</v>
+        <v>-7.495142462489087</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.72512405141438</v>
       </c>
       <c r="E13">
-        <v>-17.71361723290303</v>
+        <v>-16.67555966459877</v>
       </c>
       <c r="F13">
-        <v>-0.7332047028134061</v>
+        <v>-0.9135941302840405</v>
       </c>
       <c r="G13">
-        <v>-6.944201473843576</v>
+        <v>-6.658574225806336</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.50768463709733</v>
       </c>
       <c r="E14">
-        <v>-18.29469743214527</v>
+        <v>-17.49299450772334</v>
       </c>
       <c r="F14">
-        <v>-1.00285734487491</v>
+        <v>-0.6225662957606986</v>
       </c>
       <c r="G14">
-        <v>-6.956685541072168</v>
+        <v>-7.083251007584044</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.32706710729199</v>
       </c>
       <c r="E15">
-        <v>-19.30974129554256</v>
+        <v>-18.82773957911414</v>
       </c>
       <c r="F15">
-        <v>-0.589453965568594</v>
+        <v>-0.5435375604314173</v>
       </c>
       <c r="G15">
-        <v>-6.465936891421685</v>
+        <v>-6.369050465669375</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-19.18220707321937</v>
       </c>
       <c r="E16">
-        <v>-20.00806368684338</v>
+        <v>-18.50715531868913</v>
       </c>
       <c r="F16">
-        <v>-0.3578664624005334</v>
+        <v>-0.3525947322491173</v>
       </c>
       <c r="G16">
-        <v>-6.489170300016291</v>
+        <v>-5.520756276686526</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-19.09884436113461</v>
       </c>
       <c r="E17">
-        <v>-21.72816831086491</v>
+        <v>-20.61579395562076</v>
       </c>
       <c r="F17">
-        <v>-0.1863306257310201</v>
+        <v>-0.3084833396826409</v>
       </c>
       <c r="G17">
-        <v>-6.423959173983727</v>
+        <v>-5.947988799620551</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-19.06696180541113</v>
       </c>
       <c r="E18">
-        <v>-21.42489187809721</v>
+        <v>-20.71749442488502</v>
       </c>
       <c r="F18">
-        <v>-0.04466157576944309</v>
+        <v>0.2548636515718161</v>
       </c>
       <c r="G18">
-        <v>-5.705322501046433</v>
+        <v>-5.240932414979628</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-19.07669857857447</v>
       </c>
       <c r="E19">
-        <v>-22.7675980067935</v>
+        <v>-21.50599684757459</v>
       </c>
       <c r="F19">
-        <v>0.2262394159680792</v>
+        <v>0.5213900350551542</v>
       </c>
       <c r="G19">
-        <v>-4.945078891771581</v>
+        <v>-5.290319133334476</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-19.12493353628049</v>
       </c>
       <c r="E20">
-        <v>-22.97225786109615</v>
+        <v>-22.33281016036905</v>
       </c>
       <c r="F20">
-        <v>0.5217942783477204</v>
+        <v>0.5822750391609179</v>
       </c>
       <c r="G20">
-        <v>-5.227624021911758</v>
+        <v>-4.97519823508787</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.17598359815358</v>
       </c>
       <c r="E21">
-        <v>-23.72515289266341</v>
+        <v>-22.47719602562961</v>
       </c>
       <c r="F21">
-        <v>0.5581007932450199</v>
+        <v>1.159377071138861</v>
       </c>
       <c r="G21">
-        <v>-5.132707370755314</v>
+        <v>-5.479920697459615</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-19.22449336526348</v>
       </c>
       <c r="E22">
-        <v>-24.20252650865599</v>
+        <v>-23.56687819762132</v>
       </c>
       <c r="F22">
-        <v>1.125076033723739</v>
+        <v>1.127731779617114</v>
       </c>
       <c r="G22">
-        <v>-5.254227565865341</v>
+        <v>-4.813749550228692</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.25263752112274</v>
       </c>
       <c r="E23">
-        <v>-25.18190411076887</v>
+        <v>-23.56459131824745</v>
       </c>
       <c r="F23">
-        <v>1.269018123838598</v>
+        <v>1.432711806305808</v>
       </c>
       <c r="G23">
-        <v>-5.542678709247579</v>
+        <v>-4.773341031376348</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.24173448358737</v>
       </c>
       <c r="E24">
-        <v>-25.05850772253385</v>
+        <v>-24.38676294518405</v>
       </c>
       <c r="F24">
-        <v>1.509774825788246</v>
+        <v>1.680095447477852</v>
       </c>
       <c r="G24">
-        <v>-5.195091290897341</v>
+        <v>-4.781643879588841</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-19.20577869649811</v>
       </c>
       <c r="E25">
-        <v>-25.41702248124711</v>
+        <v>-25.38925387863208</v>
       </c>
       <c r="F25">
-        <v>1.409911821911154</v>
+        <v>1.619598119316599</v>
       </c>
       <c r="G25">
-        <v>-5.417844658052742</v>
+        <v>-4.243335932721188</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-19.13153537499988</v>
       </c>
       <c r="E26">
-        <v>-25.31430310533112</v>
+        <v>-24.12426089238142</v>
       </c>
       <c r="F26">
-        <v>1.699288720200717</v>
+        <v>1.894887801554153</v>
       </c>
       <c r="G26">
-        <v>-5.54822056248032</v>
+        <v>-5.296970019322872</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-19.03725186514325</v>
       </c>
       <c r="E27">
-        <v>-25.9997284026581</v>
+        <v>-24.00925123800862</v>
       </c>
       <c r="F27">
-        <v>1.371949400575659</v>
+        <v>1.544789915904581</v>
       </c>
       <c r="G27">
-        <v>-5.042792953908709</v>
+        <v>-5.136689957039057</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.93973689449736</v>
       </c>
       <c r="E28">
-        <v>-25.5882259695811</v>
+        <v>-24.35125518048991</v>
       </c>
       <c r="F28">
-        <v>1.46545054279925</v>
+        <v>1.888736345220964</v>
       </c>
       <c r="G28">
-        <v>-5.632503741364625</v>
+        <v>-5.406731156677409</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-18.84100059991246</v>
       </c>
       <c r="E29">
-        <v>-25.50188608415085</v>
+        <v>-24.94489283815541</v>
       </c>
       <c r="F29">
-        <v>1.435395716690878</v>
+        <v>1.84627091868385</v>
       </c>
       <c r="G29">
-        <v>-5.629822199477815</v>
+        <v>-4.870488990226262</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-18.77126612733518</v>
       </c>
       <c r="E30">
-        <v>-25.0076393740057</v>
+        <v>-24.01783269625315</v>
       </c>
       <c r="F30">
-        <v>1.529541328753848</v>
+        <v>1.508643275916022</v>
       </c>
       <c r="G30">
-        <v>-5.708255644394228</v>
+        <v>-4.93636222536668</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-18.7309773301027</v>
       </c>
       <c r="E31">
-        <v>-25.3771628530316</v>
+        <v>-23.75967345002388</v>
       </c>
       <c r="F31">
-        <v>1.313682037462741</v>
+        <v>1.65162943004805</v>
       </c>
       <c r="G31">
-        <v>-5.685545301994828</v>
+        <v>-5.360999280597916</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-18.72844221224165</v>
       </c>
       <c r="E32">
-        <v>-24.77104472100095</v>
+        <v>-23.96089619255471</v>
       </c>
       <c r="F32">
-        <v>1.274221927862984</v>
+        <v>1.349320059865982</v>
       </c>
       <c r="G32">
-        <v>-5.117664251824866</v>
+        <v>-5.005890302782453</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-18.77660931365097</v>
       </c>
       <c r="E33">
-        <v>-24.5765422338975</v>
+        <v>-22.9102358810871</v>
       </c>
       <c r="F33">
-        <v>0.9157856959368325</v>
+        <v>1.434764500729945</v>
       </c>
       <c r="G33">
-        <v>-5.325354636776583</v>
+        <v>-5.026604386221673</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-18.8559082986557</v>
       </c>
       <c r="E34">
-        <v>-23.42376483355692</v>
+        <v>-23.30656792623841</v>
       </c>
       <c r="F34">
-        <v>1.513066757846971</v>
+        <v>1.32472748841167</v>
       </c>
       <c r="G34">
-        <v>-4.800133276425671</v>
+        <v>-4.530439684068943</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-18.97113797377811</v>
       </c>
       <c r="E35">
-        <v>-23.4535712494754</v>
+        <v>-22.65385179666884</v>
       </c>
       <c r="F35">
-        <v>1.315875554345354</v>
+        <v>1.381202264464929</v>
       </c>
       <c r="G35">
-        <v>-6.252688100509531</v>
+        <v>-4.108540449998683</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-19.10578624206553</v>
       </c>
       <c r="E36">
-        <v>-23.08163862227742</v>
+        <v>-22.83580588229703</v>
       </c>
       <c r="F36">
-        <v>1.032598753610008</v>
+        <v>1.388248357593142</v>
       </c>
       <c r="G36">
-        <v>-5.26582109634387</v>
+        <v>-4.400110127278915</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-19.23762008250573</v>
       </c>
       <c r="E37">
-        <v>-23.35152208771255</v>
+        <v>-21.57769164806403</v>
       </c>
       <c r="F37">
-        <v>1.294031505933531</v>
+        <v>1.182712180875723</v>
       </c>
       <c r="G37">
-        <v>-4.688855909214148</v>
+        <v>-4.351176953662947</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-19.37129456955191</v>
       </c>
       <c r="E38">
-        <v>-22.56453217534154</v>
+        <v>-21.57520551583382</v>
       </c>
       <c r="F38">
-        <v>1.118187330402058</v>
+        <v>0.7414325817303982</v>
       </c>
       <c r="G38">
-        <v>-5.068717836026742</v>
+        <v>-4.269611732666384</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-19.48048949278625</v>
       </c>
       <c r="E39">
-        <v>-22.29665482389181</v>
+        <v>-21.05587105968617</v>
       </c>
       <c r="F39">
-        <v>0.865369599067649</v>
+        <v>1.034775703144565</v>
       </c>
       <c r="G39">
-        <v>-4.695301541379108</v>
+        <v>-3.517482270508284</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-19.56939487962288</v>
       </c>
       <c r="E40">
-        <v>-21.26488277751019</v>
+        <v>-20.78026813157934</v>
       </c>
       <c r="F40">
-        <v>1.091293554302769</v>
+        <v>1.110438781716272</v>
       </c>
       <c r="G40">
-        <v>-4.873034799745961</v>
+        <v>-3.791479572066064</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-19.63742035196362</v>
       </c>
       <c r="E41">
-        <v>-20.69519621887125</v>
+        <v>-20.02456997460134</v>
       </c>
       <c r="F41">
-        <v>0.9357178723829942</v>
+        <v>0.9919921835247758</v>
       </c>
       <c r="G41">
-        <v>-4.522020966762576</v>
+        <v>-3.193684432403248</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-19.6724695701195</v>
       </c>
       <c r="E42">
-        <v>-20.22566139138595</v>
+        <v>-19.80491181438528</v>
       </c>
       <c r="F42">
-        <v>0.8080001862193664</v>
+        <v>0.8470610227309743</v>
       </c>
       <c r="G42">
-        <v>-3.757000240274555</v>
+        <v>-3.410962157236695</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-19.69224480969553</v>
       </c>
       <c r="E43">
-        <v>-20.46418970279197</v>
+        <v>-19.35598607210889</v>
       </c>
       <c r="F43">
-        <v>0.9152953024343752</v>
+        <v>0.8525398447330902</v>
       </c>
       <c r="G43">
-        <v>-3.875650192402034</v>
+        <v>-2.9018267376611</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-19.68609545018048</v>
       </c>
       <c r="E44">
-        <v>-19.36111683315958</v>
+        <v>-19.60958514501243</v>
       </c>
       <c r="F44">
-        <v>0.8995430679027397</v>
+        <v>0.6873816086977304</v>
       </c>
       <c r="G44">
-        <v>-3.756420894805182</v>
+        <v>-3.166481679707057</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-19.66103883311582</v>
       </c>
       <c r="E45">
-        <v>-19.88824932154844</v>
+        <v>-18.76168725723826</v>
       </c>
       <c r="F45">
-        <v>0.8928266650008414</v>
+        <v>0.4078722229103156</v>
       </c>
       <c r="G45">
-        <v>-3.853343736558425</v>
+        <v>-2.974989794078994</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-19.62908417931333</v>
       </c>
       <c r="E46">
-        <v>-19.55075573917879</v>
+        <v>-17.89177192883879</v>
       </c>
       <c r="F46">
-        <v>0.7000937348610916</v>
+        <v>0.524556055268654</v>
       </c>
       <c r="G46">
-        <v>-3.804301314939662</v>
+        <v>-2.876335537008712</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-19.57865445930729</v>
       </c>
       <c r="E47">
-        <v>-18.5071960749552</v>
+        <v>-17.60056840777555</v>
       </c>
       <c r="F47">
-        <v>0.4978991922465659</v>
+        <v>0.261842646940402</v>
       </c>
       <c r="G47">
-        <v>-3.596955226724028</v>
+        <v>-2.828130683411384</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-19.5273511181458</v>
       </c>
       <c r="E48">
-        <v>-18.59512545476214</v>
+        <v>-17.65243754905941</v>
       </c>
       <c r="F48">
-        <v>0.3832059267571548</v>
+        <v>0.3898303808773424</v>
       </c>
       <c r="G48">
-        <v>-3.495463832126592</v>
+        <v>-2.810273600772556</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-19.47199517582904</v>
       </c>
       <c r="E49">
-        <v>-18.14331960301687</v>
+        <v>-16.50987185760612</v>
       </c>
       <c r="F49">
-        <v>0.2369717440387496</v>
+        <v>0.1531459330798564</v>
       </c>
       <c r="G49">
-        <v>-4.116787018937008</v>
+        <v>-2.494434314143927</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-19.40814368181654</v>
       </c>
       <c r="E50">
-        <v>-17.64184997682947</v>
+        <v>-16.9558948480436</v>
       </c>
       <c r="F50">
-        <v>0.2910086348255698</v>
+        <v>-0.08213029013287033</v>
       </c>
       <c r="G50">
-        <v>-3.993548650692099</v>
+        <v>-2.743327748877414</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-19.35190713919628</v>
       </c>
       <c r="E51">
-        <v>-16.39944501892908</v>
+        <v>-15.87276537794099</v>
       </c>
       <c r="F51">
-        <v>-0.02985119497479074</v>
+        <v>-0.2014085691967767</v>
       </c>
       <c r="G51">
-        <v>-4.018192351686434</v>
+        <v>-2.849569776323705</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-19.28679043527062</v>
       </c>
       <c r="E52">
-        <v>-16.20700751597313</v>
+        <v>-16.35114431516327</v>
       </c>
       <c r="F52">
-        <v>0.1679132387695632</v>
+        <v>0.07292766216015513</v>
       </c>
       <c r="G52">
-        <v>-3.954146537683693</v>
+        <v>-2.751468380358482</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-19.22565228131458</v>
       </c>
       <c r="E53">
-        <v>-15.62100939395856</v>
+        <v>-15.9328718134448</v>
       </c>
       <c r="F53">
-        <v>0.05254899568388448</v>
+        <v>-0.08368762085013341</v>
       </c>
       <c r="G53">
-        <v>-3.488660661043389</v>
+        <v>-2.685485897215267</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-19.17031456808053</v>
       </c>
       <c r="E54">
-        <v>-15.52541783613065</v>
+        <v>-15.45953306779305</v>
       </c>
       <c r="F54">
-        <v>0.02903992879243452</v>
+        <v>-0.06825596450338142</v>
       </c>
       <c r="G54">
-        <v>-3.814544142838166</v>
+        <v>-2.987910853318769</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-19.11173221015175</v>
       </c>
       <c r="E55">
-        <v>-15.7136031019934</v>
+        <v>-15.3271386017048</v>
       </c>
       <c r="F55">
-        <v>0.01673701612605626</v>
+        <v>-0.09361891764229668</v>
       </c>
       <c r="G55">
-        <v>-4.165134225992524</v>
+        <v>-2.873160723836551</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-19.06807757442469</v>
       </c>
       <c r="E56">
-        <v>-14.81605049672512</v>
+        <v>-14.69204276449907</v>
       </c>
       <c r="F56">
-        <v>-0.04081215244863379</v>
+        <v>-0.1293116122941218</v>
       </c>
       <c r="G56">
-        <v>-5.017596391809316</v>
+        <v>-3.449400901493172</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-19.02416067665465</v>
       </c>
       <c r="E57">
-        <v>-13.85945564734483</v>
+        <v>-14.26946368399931</v>
       </c>
       <c r="F57">
-        <v>-0.1084094176192819</v>
+        <v>-0.1721174978337862</v>
       </c>
       <c r="G57">
-        <v>-4.693619784245159</v>
+        <v>-3.353451360128476</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-18.98622547886247</v>
       </c>
       <c r="E58">
-        <v>-14.68366055911087</v>
+        <v>-14.17292567510379</v>
       </c>
       <c r="F58">
-        <v>-0.1327833000792545</v>
+        <v>-0.4664206970677974</v>
       </c>
       <c r="G58">
-        <v>-5.067324096354708</v>
+        <v>-3.721699893189306</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-18.95820890623375</v>
       </c>
       <c r="E59">
-        <v>-14.37202909179903</v>
+        <v>-13.65950087753615</v>
       </c>
       <c r="F59">
-        <v>-0.05887470366667701</v>
+        <v>-0.2573681007254945</v>
       </c>
       <c r="G59">
-        <v>-5.241597834633022</v>
+        <v>-3.684635025331626</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-18.92332253439672</v>
       </c>
       <c r="E60">
-        <v>-13.79179118872222</v>
+        <v>-13.49389458307564</v>
       </c>
       <c r="F60">
-        <v>-0.09025243251731949</v>
+        <v>-0.2616557304023848</v>
       </c>
       <c r="G60">
-        <v>-4.895248560314471</v>
+        <v>-4.145936372410291</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-18.89249300750465</v>
       </c>
       <c r="E61">
-        <v>-14.34388462584136</v>
+        <v>-13.17496774413744</v>
       </c>
       <c r="F61">
-        <v>-0.1838065902546901</v>
+        <v>-0.2878470509440996</v>
       </c>
       <c r="G61">
-        <v>-5.395803045852274</v>
+        <v>-4.233890946297648</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-18.85246227575089</v>
       </c>
       <c r="E62">
-        <v>-12.96413105128832</v>
+        <v>-12.51697141387492</v>
       </c>
       <c r="F62">
-        <v>-0.5166437843321287</v>
+        <v>-0.4321685333294406</v>
       </c>
       <c r="G62">
-        <v>-5.880599334623147</v>
+        <v>-4.138163211484082</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-18.79534293937412</v>
       </c>
       <c r="E63">
-        <v>-12.51989680808388</v>
+        <v>-12.98003505200326</v>
       </c>
       <c r="F63">
-        <v>-0.3331985095125669</v>
+        <v>-0.3429641328241703</v>
       </c>
       <c r="G63">
-        <v>-5.760433152638681</v>
+        <v>-4.068188210420507</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-18.72852919455212</v>
       </c>
       <c r="E64">
-        <v>-12.56846922029015</v>
+        <v>-12.44326597092608</v>
       </c>
       <c r="F64">
-        <v>-0.392710080464489</v>
+        <v>-0.6687245841794927</v>
       </c>
       <c r="G64">
-        <v>-5.881635535376939</v>
+        <v>-4.896231792339634</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-18.63214233375873</v>
       </c>
       <c r="E65">
-        <v>-12.35044583919086</v>
+        <v>-11.85322845009667</v>
       </c>
       <c r="F65">
-        <v>-0.4890028208355147</v>
+        <v>-0.6158026759168407</v>
       </c>
       <c r="G65">
-        <v>-6.076292302540545</v>
+        <v>-4.376532421948226</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-18.51550608248989</v>
       </c>
       <c r="E66">
-        <v>-12.47095758948298</v>
+        <v>-12.47597061020947</v>
       </c>
       <c r="F66">
-        <v>-0.4080994900736982</v>
+        <v>-0.3237708601013057</v>
       </c>
       <c r="G66">
-        <v>-6.063109710203167</v>
+        <v>-5.097555998219333</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-18.37576476453869</v>
       </c>
       <c r="E67">
-        <v>-12.47608835053367</v>
+        <v>-12.38668268820024</v>
       </c>
       <c r="F67">
-        <v>-0.3794909934506145</v>
+        <v>-0.757648168135214</v>
       </c>
       <c r="G67">
-        <v>-6.191250996391737</v>
+        <v>-4.879841281374702</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-18.20537408496973</v>
       </c>
       <c r="E68">
-        <v>-11.59729721307917</v>
+        <v>-12.7324497925819</v>
       </c>
       <c r="F68">
-        <v>-0.5507186774462862</v>
+        <v>-0.977144820692013</v>
       </c>
       <c r="G68">
-        <v>-6.299601841346544</v>
+        <v>-4.67789800347916</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-18.02186643626452</v>
       </c>
       <c r="E69">
-        <v>-11.29990326804744</v>
+        <v>-12.16942461920824</v>
       </c>
       <c r="F69">
-        <v>-0.5062941620015516</v>
+        <v>-0.6130707202224078</v>
       </c>
       <c r="G69">
-        <v>-6.312906923868875</v>
+        <v>-4.626465367981043</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.81255615080443</v>
       </c>
       <c r="E70">
-        <v>-12.37434259652934</v>
+        <v>-12.61053874382141</v>
       </c>
       <c r="F70">
-        <v>-0.421205919120792</v>
+        <v>-0.8003919261196685</v>
       </c>
       <c r="G70">
-        <v>-6.142387344232095</v>
+        <v>-5.097400402578987</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.58959486672261</v>
       </c>
       <c r="E71">
-        <v>-12.02843058097943</v>
+        <v>-12.08906231946813</v>
       </c>
       <c r="F71">
-        <v>-0.7830392857658244</v>
+        <v>-0.9530211051876858</v>
       </c>
       <c r="G71">
-        <v>-6.397216587117494</v>
+        <v>-5.251267938153234</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.36033312659628</v>
       </c>
       <c r="E72">
-        <v>-11.38076822840241</v>
+        <v>-11.96203862355297</v>
       </c>
       <c r="F72">
-        <v>-0.6923968394492941</v>
+        <v>-0.7607330083432393</v>
       </c>
       <c r="G72">
-        <v>-5.546260719521071</v>
+        <v>-4.91714450851121</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-17.1186798200867</v>
       </c>
       <c r="E73">
-        <v>-11.59428577786407</v>
+        <v>-11.58295553589688</v>
       </c>
       <c r="F73">
-        <v>-0.5304286462821152</v>
+        <v>-0.8755753799651544</v>
       </c>
       <c r="G73">
-        <v>-5.776734278874052</v>
+        <v>-5.07076706371555</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-16.8854889002799</v>
       </c>
       <c r="E74">
-        <v>-13.0380900887816</v>
+        <v>-12.42985263091536</v>
       </c>
       <c r="F74">
-        <v>-0.541683674183952</v>
+        <v>-1.146545126197109</v>
       </c>
       <c r="G74">
-        <v>-5.892871526937225</v>
+        <v>-5.330770689278831</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-16.65722768299128</v>
       </c>
       <c r="E75">
-        <v>-13.54790569256513</v>
+        <v>-13.08629569459325</v>
       </c>
       <c r="F75">
-        <v>-0.6751336627749525</v>
+        <v>-1.127364278985286</v>
       </c>
       <c r="G75">
-        <v>-5.282327476402676</v>
+        <v>-4.479612878404512</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-16.43961000026538</v>
       </c>
       <c r="E76">
-        <v>-13.26732144304987</v>
+        <v>-12.95526882765531</v>
       </c>
       <c r="F76">
-        <v>-1.164955591724328</v>
+        <v>-1.135815283228647</v>
       </c>
       <c r="G76">
-        <v>-5.426260064813569</v>
+        <v>-4.671091521850419</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-16.24484387609039</v>
       </c>
       <c r="E77">
-        <v>-13.10072794125569</v>
+        <v>-13.42858945941103</v>
       </c>
       <c r="F77">
-        <v>-0.866925567545122</v>
+        <v>-1.228474804170994</v>
       </c>
       <c r="G77">
-        <v>-5.066834135614896</v>
+        <v>-4.391287523416757</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-16.06027680458938</v>
       </c>
       <c r="E78">
-        <v>-13.64197115465245</v>
+        <v>-13.74365803849469</v>
       </c>
       <c r="F78">
-        <v>-1.100756289639964</v>
+        <v>-1.288359140454176</v>
       </c>
       <c r="G78">
-        <v>-5.106550750449532</v>
+        <v>-4.438002631521413</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-15.89603052366986</v>
       </c>
       <c r="E79">
-        <v>-14.1397546029976</v>
+        <v>-14.38160228585125</v>
       </c>
       <c r="F79">
-        <v>-0.9691427915809697</v>
+        <v>-1.483163817468327</v>
       </c>
       <c r="G79">
-        <v>-4.940225632011009</v>
+        <v>-4.314621909818315</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-15.74354539255832</v>
       </c>
       <c r="E80">
-        <v>-15.12686683871558</v>
+        <v>-14.3586655650024</v>
       </c>
       <c r="F80">
-        <v>-1.291831656606712</v>
+        <v>-1.351102172644419</v>
       </c>
       <c r="G80">
-        <v>-5.03924404909061</v>
+        <v>-4.429487908394408</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-15.59017467818383</v>
       </c>
       <c r="E81">
-        <v>-15.42314677914142</v>
+        <v>-14.76558971085765</v>
       </c>
       <c r="F81">
-        <v>-1.407123831728347</v>
+        <v>-1.680321057906429</v>
       </c>
       <c r="G81">
-        <v>-4.702121265190008</v>
+        <v>-3.880976860174721</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-15.44009806947009</v>
       </c>
       <c r="E82">
-        <v>-15.90749877357982</v>
+        <v>-16.14028497994411</v>
       </c>
       <c r="F82">
-        <v>-1.454201607964248</v>
+        <v>-1.854583051698556</v>
       </c>
       <c r="G82">
-        <v>-4.750127486054978</v>
+        <v>-3.865741729602995</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-15.26973199369697</v>
       </c>
       <c r="E83">
-        <v>-17.00415479554334</v>
+        <v>-17.18817839379304</v>
       </c>
       <c r="F83">
-        <v>-1.525885209532906</v>
+        <v>-1.678569060849508</v>
       </c>
       <c r="G83">
-        <v>-4.535071137278384</v>
+        <v>-3.181210296811274</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-15.07906061269454</v>
       </c>
       <c r="E84">
-        <v>-18.49895878073525</v>
+        <v>-17.59433269906699</v>
       </c>
       <c r="F84">
-        <v>-1.834836429550621</v>
+        <v>-1.818404105381287</v>
       </c>
       <c r="G84">
-        <v>-3.775357215289814</v>
+        <v>-3.454280645618058</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-14.8618386069286</v>
       </c>
       <c r="E85">
-        <v>-18.46599148995941</v>
+        <v>-18.42523975236438</v>
       </c>
       <c r="F85">
-        <v>-1.733403669445224</v>
+        <v>-2.107844787960865</v>
       </c>
       <c r="G85">
-        <v>-3.817440870185029</v>
+        <v>-3.648298477492585</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-14.6056386083328</v>
       </c>
       <c r="E86">
-        <v>-19.95861275067962</v>
+        <v>-19.81451217928154</v>
       </c>
       <c r="F86">
-        <v>-1.850446184888975</v>
+        <v>-2.065298181418277</v>
       </c>
       <c r="G86">
-        <v>-3.82988190032161</v>
+        <v>-3.196024988099513</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-14.32429883983056</v>
       </c>
       <c r="E87">
-        <v>-21.2633566817696</v>
+        <v>-20.39370400486258</v>
       </c>
       <c r="F87">
-        <v>-1.938535602870077</v>
+        <v>-2.070016562144623</v>
       </c>
       <c r="G87">
-        <v>-3.766938497983447</v>
+        <v>-3.211316397945406</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-14.01465993035226</v>
       </c>
       <c r="E88">
-        <v>-22.12682346318215</v>
+        <v>-21.30198003658102</v>
       </c>
       <c r="F88">
-        <v>-2.069971830304872</v>
+        <v>-2.353554298611852</v>
       </c>
       <c r="G88">
-        <v>-3.722428213207946</v>
+        <v>-3.16415105564741</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-13.69177755096831</v>
       </c>
       <c r="E89">
-        <v>-23.89696772498843</v>
+        <v>-23.27481879497063</v>
       </c>
       <c r="F89">
-        <v>-2.025949073050495</v>
+        <v>-2.336484959909765</v>
       </c>
       <c r="G89">
-        <v>-3.178108315640977</v>
+        <v>-3.178303637827794</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-13.37707252036597</v>
       </c>
       <c r="E90">
-        <v>-25.86217600467511</v>
+        <v>-25.57158835607691</v>
       </c>
       <c r="F90">
-        <v>-2.417940811729249</v>
+        <v>-2.361403079753377</v>
       </c>
       <c r="G90">
-        <v>-2.982153814625976</v>
+        <v>-2.815961118009024</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-13.07527357590979</v>
       </c>
       <c r="E91">
-        <v>-26.78069544459891</v>
+        <v>-26.94814482798053</v>
       </c>
       <c r="F91">
-        <v>-2.48223371933013</v>
+        <v>-2.67976041162988</v>
       </c>
       <c r="G91">
-        <v>-3.530472851204384</v>
+        <v>-3.045696425706748</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-12.81256963531311</v>
       </c>
       <c r="E92">
-        <v>-28.57759845931651</v>
+        <v>-28.5076878775861</v>
       </c>
       <c r="F92">
-        <v>-2.556157226355958</v>
+        <v>-2.611092895774815</v>
       </c>
       <c r="G92">
-        <v>-2.930257702752361</v>
+        <v>-2.466642284341745</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-12.5991293630273</v>
       </c>
       <c r="E93">
-        <v>-30.20256663714789</v>
+        <v>-30.34736459354315</v>
       </c>
       <c r="F93">
-        <v>-2.24048546159933</v>
+        <v>-2.958476221445413</v>
       </c>
       <c r="G93">
-        <v>-3.743443556291239</v>
+        <v>-3.175509537392649</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-12.44374488702031</v>
       </c>
       <c r="E94">
-        <v>-32.12947987638871</v>
+        <v>-31.42492630485333</v>
       </c>
       <c r="F94">
-        <v>-2.579793861827439</v>
+        <v>-2.872214181954887</v>
       </c>
       <c r="G94">
-        <v>-3.856799946101424</v>
+        <v>-3.083171801211297</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-12.37116146539702</v>
       </c>
       <c r="E95">
-        <v>-35.02841194747994</v>
+        <v>-34.59725367297264</v>
       </c>
       <c r="F95">
-        <v>-2.745147592569859</v>
+        <v>-2.874802001721232</v>
       </c>
       <c r="G95">
-        <v>-4.238800485332387</v>
+        <v>-3.086184397652034</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-12.38412724020084</v>
       </c>
       <c r="E96">
-        <v>-36.95899325066697</v>
+        <v>-36.20552310290074</v>
       </c>
       <c r="F96">
-        <v>-2.768943274582678</v>
+        <v>-2.881824900562167</v>
       </c>
       <c r="G96">
-        <v>-3.75929444833327</v>
+        <v>-3.112768078332382</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.49347811994989</v>
       </c>
       <c r="E97">
-        <v>-39.06365362318286</v>
+        <v>-38.60396143395323</v>
       </c>
       <c r="F97">
-        <v>-2.697837045093771</v>
+        <v>-2.880646962115386</v>
       </c>
       <c r="G97">
-        <v>-4.324944190809762</v>
+        <v>-3.68993189819446</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.70984472343872</v>
       </c>
       <c r="E98">
-        <v>-42.36326507447276</v>
+        <v>-40.72182230820147</v>
       </c>
       <c r="F98">
-        <v>-2.855340337959861</v>
+        <v>-2.887775891983878</v>
       </c>
       <c r="G98">
-        <v>-4.145201431300572</v>
+        <v>-4.024207612931289</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-12.99670526995808</v>
       </c>
       <c r="E99">
-        <v>-44.6917158397367</v>
+        <v>-43.80926795952101</v>
       </c>
       <c r="F99">
-        <v>-2.872239861344374</v>
+        <v>-3.050140044769595</v>
       </c>
       <c r="G99">
-        <v>-5.319776367542911</v>
+        <v>-3.874968220020944</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.36986447768466</v>
       </c>
       <c r="E100">
-        <v>-46.71761472807418</v>
+        <v>-46.02664884279882</v>
       </c>
       <c r="F100">
-        <v>-2.605527923562808</v>
+        <v>-3.050285009065085</v>
       </c>
       <c r="G100">
-        <v>-5.393816718528711</v>
+        <v>-4.284462839955554</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.74694147827356</v>
       </c>
       <c r="E101">
-        <v>-49.43831964764554</v>
+        <v>-48.56545741478557</v>
       </c>
       <c r="F101">
-        <v>-2.839728097519298</v>
+        <v>-2.999360294610583</v>
       </c>
       <c r="G101">
-        <v>-5.510937198617047</v>
+        <v>-5.016619780875231</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.16818178074284</v>
       </c>
       <c r="E102">
-        <v>-51.20923601427012</v>
+        <v>-50.57404281487322</v>
       </c>
       <c r="F102">
-        <v>-2.811998498710585</v>
+        <v>-3.281706010385183</v>
       </c>
       <c r="G102">
-        <v>-5.569755661213279</v>
+        <v>-4.423773906793625</v>
       </c>
     </row>
   </sheetData>
